--- a/jogos_2025-08-23.xlsx
+++ b/jogos_2025-08-23.xlsx
@@ -51705,12 +51705,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G364" t="n">
@@ -51731,13 +51731,13 @@
         </is>
       </c>
       <c r="L364" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="M364" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N364" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="O364" t="n">
         <v>0</v>
@@ -51767,10 +51767,10 @@
         <v>0</v>
       </c>
       <c r="X364" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Y364" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Z364" t="n">
         <v>0</v>
@@ -52128,12 +52128,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -52154,13 +52154,13 @@
         </is>
       </c>
       <c r="L367" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="M367" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N367" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="O367" t="n">
         <v>0</v>
@@ -52190,10 +52190,10 @@
         <v>0</v>
       </c>
       <c r="X367" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Y367" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Z367" t="n">
         <v>0</v>

--- a/jogos_2025-08-23.xlsx
+++ b/jogos_2025-08-23.xlsx
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="N5" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="M6" t="n">
-        <v>3.21</v>
+        <v>3.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="N7" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1430,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>3.02</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,13 +1676,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1994,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.41</v>
+        <v>3.29</v>
       </c>
       <c r="M13" t="n">
-        <v>3.26</v>
+        <v>3.41</v>
       </c>
       <c r="N13" t="n">
-        <v>2.51</v>
+        <v>1.91</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N16" t="n">
-        <v>3.28</v>
+        <v>2.51</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.13</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.03</v>
+        <v>3.28</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>3.13</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.29</v>
+        <v>2.61</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>3.51</v>
+        <v>3.98</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="N23" t="n">
-        <v>3.95</v>
+        <v>3.51</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="N24" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.86</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>3.04</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.93</v>
+        <v>2.86</v>
       </c>
       <c r="M27" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="N27" t="n">
-        <v>3.51</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="M28" t="n">
-        <v>3.37</v>
+        <v>3.17</v>
       </c>
       <c r="N28" t="n">
         <v>3.51</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.21</v>
+        <v>3.51</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,16 +5378,16 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,31 +6047,31 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -6083,22 +6083,22 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO40" s="3" t="n">
         <v>45892.33333333334</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,31 +6188,31 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6236,10 +6236,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
@@ -6258,13 +6258,13 @@
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
@@ -6273,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO41" s="3" t="n">
         <v>45892.33333333334</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.64</v>
+        <v>1.81</v>
       </c>
       <c r="M45" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.44</v>
+        <v>3.77</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.81</v>
+        <v>2.64</v>
       </c>
       <c r="M46" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="N46" t="n">
-        <v>3.77</v>
+        <v>2.44</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.2</v>
+        <v>3.77</v>
       </c>
       <c r="M49" t="n">
-        <v>3.53</v>
+        <v>3.11</v>
       </c>
       <c r="N49" t="n">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.77</v>
+        <v>1.5</v>
       </c>
       <c r="M50" t="n">
-        <v>3.11</v>
+        <v>4.7</v>
       </c>
       <c r="N50" t="n">
-        <v>2.07</v>
+        <v>5.7</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,16 +7493,16 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="Y50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA50" t="n">
         <v>1.7</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="M52" t="n">
-        <v>4.7</v>
+        <v>3.53</v>
       </c>
       <c r="N52" t="n">
-        <v>5.7</v>
+        <v>1.67</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,16 +7775,16 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.7</v>
+        <v>1.87</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>7.7</v>
+        <v>3.1</v>
       </c>
       <c r="M54" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="N54" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,16 +8057,16 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,52 +8162,52 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="M55" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="N55" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z55" t="n">
         <v>2.15</v>
       </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AA55" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8339,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="M57" t="n">
-        <v>2.9</v>
+        <v>3.47</v>
       </c>
       <c r="N57" t="n">
-        <v>4.03</v>
+        <v>4.4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8480,10 +8480,10 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -8549,22 +8549,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="M58" t="n">
-        <v>3.26</v>
+        <v>2.9</v>
       </c>
       <c r="N58" t="n">
-        <v>2.46</v>
+        <v>4.03</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8627,10 +8627,10 @@
         <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
@@ -8690,22 +8690,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8768,10 +8768,10 @@
         <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB59" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8972,22 +8972,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9536,22 +9536,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9677,22 +9677,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9959,22 +9959,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10172,10 +10172,10 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10946,22 +10946,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11024,10 +11024,10 @@
         <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB75" t="n">
         <v>0</v>
@@ -11087,22 +11087,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11123,13 +11123,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="M76" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -11159,16 +11159,16 @@
         <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
@@ -11228,22 +11228,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11441,10 +11441,10 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,22 +12074,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,16 +12569,16 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -12638,22 +12638,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="M88" t="n">
-        <v>3.96</v>
+        <v>3.57</v>
       </c>
       <c r="N88" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -13061,22 +13061,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13133,16 +13133,16 @@
         <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
         <v>0</v>
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="M91" t="n">
-        <v>3.57</v>
+        <v>4.7</v>
       </c>
       <c r="N91" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13274,16 +13274,16 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB91" t="n">
         <v>0</v>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -26607,12 +26607,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -26748,12 +26748,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -31250,7 +31250,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -31260,12 +31260,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -31286,13 +31286,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.42</v>
+        <v>1.36</v>
       </c>
       <c r="M219" t="n">
-        <v>3.21</v>
+        <v>4.4</v>
       </c>
       <c r="N219" t="n">
-        <v>2.52</v>
+        <v>6.4</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -31322,16 +31322,16 @@
         <v>0</v>
       </c>
       <c r="X219" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="Y219" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="Z219" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB219" t="n">
         <v>0</v>
@@ -33506,7 +33506,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -33542,13 +33542,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>1.36</v>
+        <v>1.97</v>
       </c>
       <c r="M235" t="n">
-        <v>4.4</v>
+        <v>3.31</v>
       </c>
       <c r="N235" t="n">
-        <v>6.4</v>
+        <v>3.21</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -33578,16 +33578,16 @@
         <v>0</v>
       </c>
       <c r="X235" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="Y235" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="Z235" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA235" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB235" t="n">
         <v>0</v>
@@ -33798,12 +33798,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -33824,13 +33824,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="M237" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="N237" t="n">
-        <v>3.21</v>
+        <v>2.52</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -33860,10 +33860,10 @@
         <v>0</v>
       </c>
       <c r="X237" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Y237" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Z237" t="n">
         <v>0</v>
@@ -48321,12 +48321,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -48347,13 +48347,13 @@
         </is>
       </c>
       <c r="L340" t="n">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="M340" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="N340" t="n">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="O340" t="n">
         <v>0</v>
@@ -48383,16 +48383,16 @@
         <v>0</v>
       </c>
       <c r="X340" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Y340" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Z340" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA340" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB340" t="n">
         <v>0</v>
@@ -48744,12 +48744,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -48770,13 +48770,13 @@
         </is>
       </c>
       <c r="L343" t="n">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="M343" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="N343" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="O343" t="n">
         <v>0</v>
@@ -48806,16 +48806,16 @@
         <v>0</v>
       </c>
       <c r="X343" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Y343" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Z343" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA343" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB343" t="n">
         <v>0</v>
@@ -50859,12 +50859,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -50885,52 +50885,52 @@
         </is>
       </c>
       <c r="L358" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M358" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N358" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O358" t="n">
+        <v>0</v>
+      </c>
+      <c r="P358" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>0</v>
+      </c>
+      <c r="R358" t="n">
+        <v>0</v>
+      </c>
+      <c r="S358" t="n">
+        <v>0</v>
+      </c>
+      <c r="T358" t="n">
+        <v>0</v>
+      </c>
+      <c r="U358" t="n">
+        <v>0</v>
+      </c>
+      <c r="V358" t="n">
+        <v>0</v>
+      </c>
+      <c r="W358" t="n">
+        <v>0</v>
+      </c>
+      <c r="X358" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA358" t="n">
         <v>1.7</v>
-      </c>
-      <c r="M358" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N358" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O358" t="n">
-        <v>0</v>
-      </c>
-      <c r="P358" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
-      <c r="R358" t="n">
-        <v>0</v>
-      </c>
-      <c r="S358" t="n">
-        <v>0</v>
-      </c>
-      <c r="T358" t="n">
-        <v>0</v>
-      </c>
-      <c r="U358" t="n">
-        <v>0</v>
-      </c>
-      <c r="V358" t="n">
-        <v>0</v>
-      </c>
-      <c r="W358" t="n">
-        <v>0</v>
-      </c>
-      <c r="X358" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Y358" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z358" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA358" t="n">
-        <v>1.6</v>
       </c>
       <c r="AB358" t="n">
         <v>0</v>
@@ -51000,12 +51000,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="L359" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="M359" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="N359" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="O359" t="n">
         <v>0</v>
@@ -51062,16 +51062,16 @@
         <v>0</v>
       </c>
       <c r="X359" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Y359" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z359" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AA359" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB359" t="n">
         <v>0</v>
@@ -52118,7 +52118,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -52128,12 +52128,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -52154,13 +52154,13 @@
         </is>
       </c>
       <c r="L367" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="M367" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="N367" t="n">
-        <v>2.55</v>
+        <v>6.4</v>
       </c>
       <c r="O367" t="n">
         <v>0</v>
@@ -52190,16 +52190,16 @@
         <v>0</v>
       </c>
       <c r="X367" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y367" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z367" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA367" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB367" t="n">
         <v>0</v>
@@ -52269,12 +52269,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -52295,13 +52295,13 @@
         </is>
       </c>
       <c r="L368" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="M368" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="N368" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="O368" t="n">
         <v>0</v>
@@ -52337,10 +52337,10 @@
         <v>0</v>
       </c>
       <c r="Z368" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AA368" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB368" t="n">
         <v>0</v>
@@ -52541,7 +52541,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -52551,12 +52551,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G370" t="n">
@@ -52577,13 +52577,13 @@
         </is>
       </c>
       <c r="L370" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="M370" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N370" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="O370" t="n">
         <v>0</v>
@@ -52613,16 +52613,16 @@
         <v>0</v>
       </c>
       <c r="X370" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y370" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z370" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA370" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB370" t="n">
         <v>0</v>
